--- a/library/interfaces.xlsx
+++ b/library/interfaces.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10112"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/garou/Documents/work/elem_altium_db2/library/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D73F18A2-F69E-4FA2-9FB0-3522D921929D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC3F417B-5810-1143-80B8-53D6BEF3E811}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11580" yWindow="4545" windowWidth="13530" windowHeight="10395" activeTab="4" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" activeTab="4" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
   <sheets>
     <sheet name="can" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="95">
   <si>
     <t>Part Number</t>
   </si>
@@ -292,9 +292,6 @@
     <t>16-SSOP</t>
   </si>
   <si>
-    <t>FT230XS-R 16-SSOP</t>
-  </si>
-  <si>
     <t>FT230X</t>
   </si>
   <si>
@@ -320,6 +317,12 @@
   </si>
   <si>
     <t>ISO1050</t>
+  </si>
+  <si>
+    <t>SSOP-16</t>
+  </si>
+  <si>
+    <t>FT230XS-R SSOP-16</t>
   </si>
 </sst>
 </file>
@@ -376,8 +379,8 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Accent 3 2" xfId="1" xr:uid="{07D6D35A-A25D-4183-ACA2-756DA14CBAEA}"/>
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -393,9 +396,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office 2013–2022">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -433,7 +436,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -539,7 +542,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -681,7 +684,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -690,12 +693,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67671D6E-5D55-4C0C-9FE7-A86F937C6875}">
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.5703125" customWidth="1"/>
+    <col min="1" max="2" width="20.83203125" customWidth="1"/>
+    <col min="3" max="3" width="25.83203125" customWidth="1"/>
+    <col min="4" max="8" width="20.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -721,7 +726,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -744,7 +749,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>20</v>
       </c>
@@ -767,7 +772,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>24</v>
       </c>
@@ -790,7 +795,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -813,7 +818,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>30</v>
       </c>
@@ -836,21 +841,21 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B7" t="s">
         <v>52</v>
       </c>
       <c r="C7" t="s">
+        <v>91</v>
+      </c>
+      <c r="D7" t="s">
+        <v>90</v>
+      </c>
+      <c r="E7" t="s">
         <v>92</v>
-      </c>
-      <c r="D7" t="s">
-        <v>91</v>
-      </c>
-      <c r="E7" t="s">
-        <v>93</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>55</v>
@@ -867,12 +872,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E834B2D-3CFC-49B2-A2B4-67F2231F306F}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" customWidth="1"/>
+    <col min="1" max="2" width="20.83203125" customWidth="1"/>
+    <col min="3" max="3" width="25.83203125" customWidth="1"/>
+    <col min="4" max="8" width="20.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -898,7 +905,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>20</v>
       </c>
@@ -929,17 +936,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE4D8C3D-D832-496B-AB92-259D2AD291EC}">
   <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.5703125" customWidth="1"/>
-    <col min="2" max="2" width="11.42578125" customWidth="1"/>
-    <col min="3" max="3" width="22.5703125" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" customWidth="1"/>
-    <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="10.140625" customWidth="1"/>
+    <col min="1" max="2" width="20.83203125" customWidth="1"/>
+    <col min="3" max="3" width="25.83203125" customWidth="1"/>
+    <col min="4" max="8" width="20.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -965,7 +969,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>35</v>
       </c>
@@ -989,7 +993,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>40</v>
       </c>
@@ -1012,7 +1016,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>42</v>
       </c>
@@ -1043,16 +1047,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDD41208-6905-41A5-8CDA-45891F714057}">
   <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="3" max="3" width="22.7109375" customWidth="1"/>
-    <col min="4" max="4" width="16.85546875" customWidth="1"/>
-    <col min="5" max="5" width="13.85546875" customWidth="1"/>
-    <col min="6" max="6" width="15.7109375" customWidth="1"/>
+    <col min="1" max="2" width="20.83203125" customWidth="1"/>
+    <col min="3" max="3" width="25.83203125" customWidth="1"/>
+    <col min="4" max="8" width="20.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1078,7 +1080,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>47</v>
       </c>
@@ -1101,7 +1103,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>51</v>
       </c>
@@ -1124,7 +1126,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>56</v>
       </c>
@@ -1147,7 +1149,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>59</v>
       </c>
@@ -1171,7 +1173,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>64</v>
       </c>
@@ -1195,7 +1197,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>66</v>
       </c>
@@ -1218,7 +1220,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>69</v>
       </c>
@@ -1241,7 +1243,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>73</v>
       </c>
@@ -1272,14 +1274,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A36817BF-F161-418A-9B8F-87A18459EBCD}">
   <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.140625" customWidth="1"/>
-    <col min="3" max="3" width="27.7109375" customWidth="1"/>
-    <col min="4" max="4" width="21.5703125" customWidth="1"/>
+    <col min="1" max="2" width="20.83203125" customWidth="1"/>
+    <col min="3" max="3" width="25.83203125" customWidth="1"/>
+    <col min="4" max="8" width="20.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1305,7 +1307,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>76</v>
       </c>
@@ -1328,44 +1330,44 @@
         <v>81</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>82</v>
       </c>
       <c r="B3" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="C3" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="D3" t="s">
         <v>82</v>
       </c>
       <c r="E3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>83</v>
       </c>
       <c r="G3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="B4" t="s">
         <v>87</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>88</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E4" t="s">
         <v>89</v>
-      </c>
-      <c r="D4" t="s">
-        <v>87</v>
-      </c>
-      <c r="E4" t="s">
-        <v>90</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>12</v>

--- a/library/interfaces.xlsx
+++ b/library/interfaces.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10112"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/garou/Documents/work/elem_altium_db2/library/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC3F417B-5810-1143-80B8-53D6BEF3E811}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3A861B4-0455-451D-B72D-E2DE01A29E1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" activeTab="4" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
   <sheets>
     <sheet name="can" sheetId="1" r:id="rId1"/>
@@ -33,12 +33,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="93">
   <si>
     <t>Part Number</t>
   </si>
@@ -91,9 +94,6 @@
     <t>Н02.8-1В</t>
   </si>
   <si>
-    <t>5559ИН14АУ Н02.8-1В</t>
-  </si>
-  <si>
     <t>5559ИН14</t>
   </si>
   <si>
@@ -115,18 +115,12 @@
     <t>SN65HVD232D</t>
   </si>
   <si>
-    <t>SN65HVD232D SOIC-8</t>
-  </si>
-  <si>
     <t>SN65HVD23x</t>
   </si>
   <si>
     <t>TCAN1051VDQ1</t>
   </si>
   <si>
-    <t>TCAN1051VDQ1 SOIC-8</t>
-  </si>
-  <si>
     <t>TCAN1051</t>
   </si>
   <si>
@@ -136,9 +130,6 @@
     <t>SOP-8</t>
   </si>
   <si>
-    <t>TPT1051V-SO1R SOP-8</t>
-  </si>
-  <si>
     <t>TPT1051</t>
   </si>
   <si>
@@ -313,9 +304,6 @@
     <t>ISO1050DW</t>
   </si>
   <si>
-    <t>ISO1050DW SOIC-16W</t>
-  </si>
-  <si>
     <t>ISO1050</t>
   </si>
   <si>
@@ -323,6 +311,15 @@
   </si>
   <si>
     <t>FT230XS-R SSOP-16</t>
+  </si>
+  <si>
+    <t>ISO1050DUBR</t>
+  </si>
+  <si>
+    <t>8-LSOP</t>
+  </si>
+  <si>
+    <t>ISO1050_8-LSOP</t>
   </si>
 </sst>
 </file>
@@ -379,8 +376,8 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
+    <cellStyle name="Accent 3 2" xfId="1" xr:uid="{07D6D35A-A25D-4183-ACA2-756DA14CBAEA}"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Accent 3 2" xfId="1" xr:uid="{07D6D35A-A25D-4183-ACA2-756DA14CBAEA}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -692,15 +689,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67671D6E-5D55-4C0C-9FE7-A86F937C6875}">
-  <dimension ref="A1:H7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="25.83203125" customWidth="1"/>
-    <col min="4" max="8" width="20.83203125" customWidth="1"/>
+    <col min="1" max="2" width="20.85546875" customWidth="1"/>
+    <col min="3" max="3" width="25.85546875" customWidth="1"/>
+    <col min="4" max="8" width="20.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -726,67 +723,70 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>15</v>
       </c>
       <c r="B2" t="s">
         <v>16</v>
       </c>
-      <c r="C2" t="s">
-        <v>17</v>
+      <c r="C2" t="str">
+        <f t="shared" ref="C2:C7" si="0">_xlfn.CONCAT(D2, " ", B2)</f>
+        <v>5559ИН14АУ Н02.8-1В</v>
       </c>
       <c r="D2" t="s">
         <v>15</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
+      <c r="B3" t="s">
         <v>20</v>
       </c>
-      <c r="B3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>22</v>
+      <c r="C3" t="str">
+        <f t="shared" si="0"/>
+        <v>YT8512H QFN-32</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>24</v>
       </c>
       <c r="B4" t="s">
         <v>9</v>
       </c>
-      <c r="C4" t="s">
-        <v>25</v>
+      <c r="C4" t="str">
+        <f t="shared" si="0"/>
+        <v>SN65HVD232D SOIC-8</v>
       </c>
       <c r="D4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" t="s">
         <v>24</v>
-      </c>
-      <c r="E4" t="s">
-        <v>26</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>10</v>
@@ -795,21 +795,22 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B5" t="s">
         <v>9</v>
       </c>
-      <c r="C5" t="s">
-        <v>28</v>
+      <c r="C5" t="str">
+        <f t="shared" si="0"/>
+        <v>TCAN1051VDQ1 SOIC-8</v>
       </c>
       <c r="D5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>10</v>
@@ -818,49 +819,75 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6" t="s">
-        <v>32</v>
+        <v>28</v>
+      </c>
+      <c r="C6" t="str">
+        <f t="shared" si="0"/>
+        <v>TPT1051V-SO1R SOP-8</v>
       </c>
       <c r="D6" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E6" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>86</v>
+      </c>
+      <c r="B7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" t="str">
+        <f t="shared" si="0"/>
+        <v>ISO1050DW SOIC-16W</v>
+      </c>
+      <c r="D7" t="s">
+        <v>86</v>
+      </c>
+      <c r="E7" t="s">
+        <v>87</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="G7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>90</v>
       </c>
-      <c r="B7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="B8" t="s">
         <v>91</v>
       </c>
-      <c r="D7" t="s">
+      <c r="C8" t="str">
+        <f>_xlfn.CONCAT(D8, " ", B8)</f>
+        <v>ISO1050DUBR 8-LSOP</v>
+      </c>
+      <c r="D8" t="s">
         <v>90</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E8" t="s">
         <v>92</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G7" t="s">
+      <c r="F8" t="s">
+        <v>91</v>
+      </c>
+      <c r="G8" t="s">
         <v>8</v>
       </c>
     </row>
@@ -872,14 +899,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E834B2D-3CFC-49B2-A2B4-67F2231F306F}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="25.83203125" customWidth="1"/>
-    <col min="4" max="8" width="20.83203125" customWidth="1"/>
+    <col min="1" max="2" width="20.85546875" customWidth="1"/>
+    <col min="3" max="3" width="25.85546875" customWidth="1"/>
+    <col min="4" max="8" width="20.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -905,27 +932,27 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" t="s">
         <v>20</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>22</v>
-      </c>
       <c r="D2" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -936,14 +963,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE4D8C3D-D832-496B-AB92-259D2AD291EC}">
   <dimension ref="A1:H4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="25.83203125" customWidth="1"/>
-    <col min="4" max="8" width="20.83203125" customWidth="1"/>
+    <col min="1" max="2" width="20.85546875" customWidth="1"/>
+    <col min="3" max="3" width="25.85546875" customWidth="1"/>
+    <col min="4" max="8" width="20.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -969,74 +996,74 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+      <c r="C4" t="s">
         <v>40</v>
       </c>
-      <c r="B3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="D4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E4" t="s">
         <v>41</v>
-      </c>
-      <c r="D3" t="s">
-        <v>40</v>
-      </c>
-      <c r="E3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="H3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D4" t="s">
-        <v>42</v>
-      </c>
-      <c r="E4" t="s">
-        <v>45</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>11</v>
       </c>
       <c r="H4" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -1047,14 +1074,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDD41208-6905-41A5-8CDA-45891F714057}">
   <dimension ref="A1:H9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="25.83203125" customWidth="1"/>
-    <col min="4" max="8" width="20.83203125" customWidth="1"/>
+    <col min="1" max="2" width="20.85546875" customWidth="1"/>
+    <col min="3" max="3" width="25.85546875" customWidth="1"/>
+    <col min="4" max="8" width="20.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1080,190 +1107,190 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>47</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B3" t="s">
         <v>48</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C3" t="s">
         <v>49</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D3" t="s">
         <v>47</v>
       </c>
-      <c r="E2" t="s">
-        <v>47</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="E3" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+      <c r="F3" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="B3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>55</v>
       </c>
       <c r="G3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D4" t="s">
         <v>52</v>
       </c>
-      <c r="C4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D4" t="s">
-        <v>56</v>
-      </c>
       <c r="E4" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B5" t="s">
         <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D5" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E5" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>14</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B6" t="s">
         <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D6" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E6" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>16</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
+      <c r="D7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E7" t="s">
+        <v>58</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B8" t="s">
         <v>66</v>
       </c>
-      <c r="B7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="C8" t="s">
         <v>67</v>
       </c>
-      <c r="D7" t="s">
-        <v>66</v>
-      </c>
-      <c r="E7" t="s">
-        <v>62</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="H7" t="s">
+      <c r="D8" t="s">
+        <v>65</v>
+      </c>
+      <c r="E8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H8" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>69</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" t="s">
         <v>70</v>
       </c>
-      <c r="C8" t="s">
-        <v>71</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="D9" t="s">
         <v>69</v>
       </c>
-      <c r="E8" t="s">
-        <v>62</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="H8" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>73</v>
-      </c>
-      <c r="B9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" t="s">
-        <v>74</v>
-      </c>
-      <c r="D9" t="s">
-        <v>73</v>
-      </c>
       <c r="E9" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -1274,14 +1301,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A36817BF-F161-418A-9B8F-87A18459EBCD}">
   <dimension ref="A1:H4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="25.83203125" customWidth="1"/>
-    <col min="4" max="8" width="20.83203125" customWidth="1"/>
+    <col min="1" max="2" width="20.85546875" customWidth="1"/>
+    <col min="3" max="3" width="25.85546875" customWidth="1"/>
+    <col min="4" max="8" width="20.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1307,67 +1334,67 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B2" t="s">
+      <c r="G2" t="s">
         <v>77</v>
       </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="B3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="G3" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>82</v>
       </c>
-      <c r="B3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C3" t="s">
-        <v>94</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="B4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4" t="s">
+        <v>84</v>
+      </c>
+      <c r="D4" t="s">
         <v>82</v>
       </c>
-      <c r="E3" t="s">
-        <v>84</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="E4" t="s">
         <v>85</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>86</v>
-      </c>
-      <c r="B4" t="s">
-        <v>87</v>
-      </c>
-      <c r="C4" t="s">
-        <v>88</v>
-      </c>
-      <c r="D4" t="s">
-        <v>86</v>
-      </c>
-      <c r="E4" t="s">
-        <v>89</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>12</v>

--- a/library/interfaces.xlsx
+++ b/library/interfaces.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\elem_altium_db2\library\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3A861B4-0455-451D-B72D-E2DE01A29E1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8CC1AE4-63CF-4A38-A214-E32AC6ED9382}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
   <sheets>
     <sheet name="can" sheetId="1" r:id="rId1"/>
@@ -32,9 +32,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -393,9 +390,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office 2013–2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Стандартная">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -433,7 +430,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Стандартная">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -539,7 +536,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Стандартная">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -681,7 +678,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
